--- a/artfynd/A 12644-2024 artfynd.xlsx
+++ b/artfynd/A 12644-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>112685078</v>
       </c>
       <c r="B2" t="n">
-        <v>93488</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,7 +713,7 @@
         <v>490658</v>
       </c>
       <c r="R2" t="n">
-        <v>6296732</v>
+        <v>6296731</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,7 +760,7 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Samuel Keith</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112685079</v>
+        <v>112685075</v>
       </c>
       <c r="B3" t="n">
-        <v>5182</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skogen vid Knöpplaberg, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490669</v>
+        <v>490729</v>
       </c>
       <c r="R3" t="n">
-        <v>6296737</v>
+        <v>6296778</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>Mindre förekomst</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,7 +862,7 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Samuel Keith</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -892,12 +877,7 @@
         <v>118222962</v>
       </c>
       <c r="B4" t="n">
-        <v>56601</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,27 +964,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Samuel Keith</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Samuel Keith</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118222829</v>
+        <v>118223097</v>
       </c>
       <c r="B5" t="n">
-        <v>57309</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,16 +987,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102977</v>
+        <v>100038</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1041,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490755</v>
+        <v>490804</v>
       </c>
       <c r="R5" t="n">
-        <v>6296728</v>
+        <v>6296747</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1071,12 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,27 +1066,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Samuel Keith</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Samuel Keith</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118223096</v>
+        <v>118222829</v>
       </c>
       <c r="B6" t="n">
-        <v>57659</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>102977</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490767</v>
+        <v>490755</v>
       </c>
       <c r="R6" t="n">
-        <v>6296759</v>
+        <v>6296728</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1178,12 +1148,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,15 +1168,530 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Samuel Keith</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Samuel Keith</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118222814</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norra Rinkaby, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>490771</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6296778</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tävelsås</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sam Keith</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Emil Lundahl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118223096</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norra Rinkaby, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>490767</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6296759</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tävelsås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sam Keith</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sam Keith</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>112685079</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skogen vid Knöpplaberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>490669</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6296737</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tävelsås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sam Keith</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118222324</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Norra Rinkaby, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>490822</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6296766</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tävelsås</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sam Keith</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sam Keith</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118222956</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Norra Rinkaby, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>490738</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6296768</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tävelsås</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sam Keith</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sam Keith</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12644-2024 artfynd.xlsx
+++ b/artfynd/A 12644-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112685078</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112685075</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118222962</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118223097</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118222829</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118222814</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118223096</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112685079</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118222324</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,8 +1742,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118222956</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>